--- a/mosip_master/xlsx/registration_center_h.xlsx
+++ b/mosip_master/xlsx/registration_center_h.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F46D30C-CF4A-4D6A-A18D-2737266BD8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF714F76-0BC6-4DA7-B2ED-62F7F28BFF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="6800" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>lang_code</t>
   </si>
@@ -120,9 +120,6 @@
     <t>MyCountry</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>24:00:00</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
-  </si>
-  <si>
-    <t>KTA</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -690,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -699,37 +693,37 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>35</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>36</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>37</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>39</v>
-      </c>
-      <c r="V2" t="s">
-        <v>31</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="36" spans="6:7" x14ac:dyDescent="0.35">

--- a/mosip_master/xlsx/registration_center_h.xlsx
+++ b/mosip_master/xlsx/registration_center_h.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247A919D-CB12-4E86-A897-538B9A1ACDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F726D86-8210-4238-9ADA-E4E57C60987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="7740" windowWidth="14610" windowHeight="7845" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>lang_code</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>URE</t>
+  </si>
+  <si>
+    <t>UPO</t>
   </si>
 </sst>
 </file>
@@ -160,7 +163,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -671,8 +674,8 @@
       <c r="I2">
         <v>134.58000000000001</v>
       </c>
-      <c r="J2" s="2">
-        <v>14022</v>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="K2">
         <v>411111111</v>

--- a/mosip_master/xlsx/registration_center_h.xlsx
+++ b/mosip_master/xlsx/registration_center_h.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F726D86-8210-4238-9ADA-E4E57C60987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4170B220-EA64-4908-B56C-A04D6C88CAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="9150" windowWidth="21600" windowHeight="11055" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,13 +138,13 @@
     <t>The High Street</t>
   </si>
   <si>
-    <t>(GTM+11:00) AUSTRALIAN EASTERN STANDARD TIME</t>
-  </si>
-  <si>
     <t>URE</t>
   </si>
   <si>
     <t>UPO</t>
+  </si>
+  <si>
+    <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
   </si>
 </sst>
 </file>
@@ -669,13 +669,13 @@
         <v>36</v>
       </c>
       <c r="H2">
-        <v>-22.2333</v>
+        <v>34.521169999999998</v>
       </c>
       <c r="I2">
-        <v>134.58000000000001</v>
+        <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2">
         <v>411111111</v>
@@ -705,13 +705,13 @@
         <v>28</v>
       </c>
       <c r="T2" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" t="s">
         <v>37</v>
       </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
       <c r="V2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>29</v>

--- a/mosip_master/xlsx/registration_center_h.xlsx
+++ b/mosip_master/xlsx/registration_center_h.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4170B220-EA64-4908-B56C-A04D6C88CAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9327CCE7-60E3-41F1-9D85-1787F5557A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="9150" windowWidth="21600" windowHeight="11055" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>lang_code</t>
   </si>
@@ -129,9 +129,6 @@
     <t>17:00:00</t>
   </si>
   <si>
-    <t>John Smith</t>
-  </si>
-  <si>
     <t>Utopian Centre</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
+  </si>
+  <si>
+    <t>UPR</t>
   </si>
 </sst>
 </file>
@@ -660,13 +660,13 @@
         <v>10001</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2">
         <v>34.521169999999998</v>
@@ -675,13 +675,7 @@
         <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2">
-        <v>411111111</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -705,13 +699,13 @@
         <v>28</v>
       </c>
       <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
         <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>37</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>29</v>

--- a/mosip_master/xlsx/registration_center_h.xlsx
+++ b/mosip_master/xlsx/registration_center_h.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9327CCE7-60E3-41F1-9D85-1787F5557A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669FE5C5-F338-45D8-8AF6-9B4AF68E9512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,6 @@
     <t>17:00:00</t>
   </si>
   <si>
-    <t>Utopian Centre</t>
-  </si>
-  <si>
     <t>The High Street</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>UPR</t>
+  </si>
+  <si>
+    <t>Utopian Registration Centre</t>
   </si>
 </sst>
 </file>
@@ -660,13 +660,13 @@
         <v>10001</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2">
         <v>34.521169999999998</v>
@@ -675,7 +675,7 @@
         <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -699,13 +699,13 @@
         <v>28</v>
       </c>
       <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" t="s">
         <v>38</v>
-      </c>
-      <c r="U2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>29</v>
